--- a/四号谷地毕业.xlsx
+++ b/四号谷地毕业.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14495" windowHeight="11304" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="17184" windowHeight="8640" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="据点产出" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
     <t>蓝/紫研磨产物</t>
   </si>
   <si>
-    <t>EF01I436UOa6E9985o08</t>
+    <t>EF01Oe4o1U3oAIou9oe4</t>
   </si>
   <si>
     <t>源石研磨产物</t>
@@ -321,8 +321,8 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="#;\-;\-#"/>
+    <numFmt numFmtId="176" formatCode="#;\-;\-#"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="21">
@@ -1003,7 +1003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1032,7 +1032,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1042,18 +1042,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
@@ -1643,7 +1639,7 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2">
@@ -1668,7 +1664,7 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3">
@@ -1693,7 +1689,7 @@
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4">
@@ -1715,28 +1711,28 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="14">
-        <v>1</v>
-      </c>
-      <c r="C5" s="13">
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
         <f>VLOOKUP(A5,商品产出!A:B,2,0)*B5</f>
         <v>180</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>VLOOKUP(A5,商品产出!A:C,3,0)*B5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>VLOOKUP(A5,商品产出!A:D,4,0)*B5</f>
         <v>120</v>
       </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3"/>
@@ -1745,7 +1741,7 @@
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="3">
         <v>1.5</v>
       </c>
       <c r="C6">
@@ -1770,7 +1766,7 @@
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="3">
         <v>1</v>
       </c>
       <c r="C7">
@@ -1792,33 +1788,33 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15">
         <f>560-SUM(C2:C7)</f>
         <v>20</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <f>240-SUM(D2:D7)</f>
         <v>120</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f>1080-SUM(E2:E7)</f>
         <v>120</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <f>ROUND(SUM(F2:F7)-SUM(据点产出!C2:C4),0)</f>
         <v>1068</v>
       </c>
     </row>
     <row r="9" spans="3:5">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
@@ -2006,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11"/>
     </row>
@@ -2366,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11"/>
     </row>
@@ -2515,7 +2511,7 @@
       <c r="F37" s="11"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1"/>
+  <sheetProtection sheet="1" autoFilter="0" objects="1"/>
   <autoFilter ref="A1:F37">
     <extLst/>
   </autoFilter>
